--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121574580</v>
+        <v>121572309</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>79226</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473692</v>
+        <v>473725</v>
       </c>
       <c r="R4" t="n">
-        <v>7015631</v>
+        <v>7015461</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,9 +982,19 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121572309</v>
+        <v>121571997</v>
       </c>
       <c r="B5" t="n">
-        <v>79226</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1037,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473725</v>
+        <v>473779</v>
       </c>
       <c r="R5" t="n">
-        <v>7015461</v>
+        <v>7015441</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121571997</v>
+        <v>121574580</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,51 +1168,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473779</v>
+        <v>473692</v>
       </c>
       <c r="R6" t="n">
-        <v>7015441</v>
+        <v>7015631</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,24 +1225,9 @@
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121574426</v>
+        <v>121572309</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473705</v>
+        <v>473725</v>
       </c>
       <c r="R2" t="n">
-        <v>7015632</v>
+        <v>7015461</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,14 +748,19 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack vanligt i området.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121572058</v>
+        <v>121574426</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473765</v>
+        <v>473705</v>
       </c>
       <c r="R3" t="n">
-        <v>7015453</v>
+        <v>7015632</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,24 +865,14 @@
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om skalade granar. Uppenbart revir.</t>
+          <t>Barkflag/ringhack vanligt i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121572309</v>
+        <v>121572058</v>
       </c>
       <c r="B4" t="n">
-        <v>79226</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +915,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473725</v>
+        <v>473765</v>
       </c>
       <c r="R4" t="n">
-        <v>7015461</v>
+        <v>7015453</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om skalade granar. Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>121571997</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121572309</v>
+        <v>121572058</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473725</v>
+        <v>473765</v>
       </c>
       <c r="R2" t="n">
-        <v>7015461</v>
+        <v>7015453</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gott om skalade granar. Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121574426</v>
+        <v>121572309</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>79227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +813,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473705</v>
+        <v>473725</v>
       </c>
       <c r="R3" t="n">
-        <v>7015632</v>
+        <v>7015461</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,14 +870,19 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack vanligt i området.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121572058</v>
+        <v>121574426</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -944,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473765</v>
+        <v>473705</v>
       </c>
       <c r="R4" t="n">
-        <v>7015453</v>
+        <v>7015632</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,24 +987,14 @@
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om skalade granar. Uppenbart revir.</t>
+          <t>Barkflag/ringhack vanligt i området.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121572058</v>
+        <v>121572309</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473765</v>
+        <v>473725</v>
       </c>
       <c r="R2" t="n">
-        <v>7015453</v>
+        <v>7015461</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gott om skalade granar. Uppenbart revir.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121572309</v>
+        <v>121571997</v>
       </c>
       <c r="B3" t="n">
-        <v>79227</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,37 +803,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473725</v>
+        <v>473779</v>
       </c>
       <c r="R3" t="n">
-        <v>7015461</v>
+        <v>7015441</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121574426</v>
+        <v>121572058</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -954,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473705</v>
+        <v>473765</v>
       </c>
       <c r="R4" t="n">
-        <v>7015632</v>
+        <v>7015453</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,14 +996,24 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Barkflag/ringhack vanligt i området.</t>
+          <t>Gott om skalade granar. Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121571997</v>
+        <v>121574426</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1054,31 +1073,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473779</v>
+        <v>473705</v>
       </c>
       <c r="R5" t="n">
-        <v>7015441</v>
+        <v>7015632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,24 +1118,14 @@
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bearbetade stående döda granar.</t>
+          <t>Barkflag/ringhack vanligt i området.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121572309</v>
+        <v>121574426</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473725</v>
+        <v>473705</v>
       </c>
       <c r="R2" t="n">
-        <v>7015461</v>
+        <v>7015632</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +753,14 @@
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:35</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack vanligt i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121571997</v>
+        <v>121572058</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -820,34 +820,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473779</v>
+        <v>473765</v>
       </c>
       <c r="R3" t="n">
-        <v>7015441</v>
+        <v>7015453</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bearbetade stående döda granar.</t>
+          <t>Gott om skalade granar. Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121572058</v>
+        <v>121572309</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>79227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,42 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473765</v>
+        <v>473725</v>
       </c>
       <c r="R4" t="n">
-        <v>7015453</v>
+        <v>7015461</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gott om skalade granar. Uppenbart revir.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121574426</v>
+        <v>121571997</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1073,22 +1054,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473705</v>
+        <v>473779</v>
       </c>
       <c r="R5" t="n">
-        <v>7015632</v>
+        <v>7015441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,14 +1108,24 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Barkflag/ringhack vanligt i området.</t>
+          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121574426</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121572058</v>
+        <v>121571997</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,25 +820,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473765</v>
+        <v>473779</v>
       </c>
       <c r="R3" t="n">
-        <v>7015453</v>
+        <v>7015441</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om skalade granar. Uppenbart revir.</t>
+          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121572309</v>
+        <v>121572058</v>
       </c>
       <c r="B4" t="n">
-        <v>79227</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +934,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473725</v>
+        <v>473765</v>
       </c>
       <c r="R4" t="n">
-        <v>7015461</v>
+        <v>7015453</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om skalade granar. Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121571997</v>
+        <v>121572309</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>79234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,51 +1056,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473779</v>
+        <v>473725</v>
       </c>
       <c r="R5" t="n">
-        <v>7015441</v>
+        <v>7015461</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetade stående döda granar.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
         <v>121574580</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121572058</v>
+        <v>121571997</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -820,25 +820,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473765</v>
+        <v>473779</v>
       </c>
       <c r="R3" t="n">
-        <v>7015453</v>
+        <v>7015441</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om skalade granar. Uppenbart revir.</t>
+          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121571997</v>
+        <v>121572058</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1054,34 +1063,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473779</v>
+        <v>473765</v>
       </c>
       <c r="R5" t="n">
-        <v>7015441</v>
+        <v>7015453</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bearbetade stående döda granar.</t>
+          <t>Gott om skalade granar. Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121574426</v>
+        <v>121571997</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -708,22 +708,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473705</v>
+        <v>473779</v>
       </c>
       <c r="R2" t="n">
-        <v>7015632</v>
+        <v>7015441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,14 +762,24 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Barkflag/ringhack vanligt i området.</t>
+          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121571997</v>
+        <v>121572309</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>79234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,51 +822,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473779</v>
+        <v>473725</v>
       </c>
       <c r="R3" t="n">
-        <v>7015441</v>
+        <v>7015461</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetade stående döda granar.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121572309</v>
+        <v>121574580</v>
       </c>
       <c r="B4" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473725</v>
+        <v>473692</v>
       </c>
       <c r="R4" t="n">
-        <v>7015461</v>
+        <v>7015631</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,19 +991,9 @@
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1027,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1152,14 +1142,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121574580</v>
+        <v>121574426</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1168,37 +1158,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473692</v>
+        <v>473705</v>
       </c>
       <c r="R6" t="n">
-        <v>7015631</v>
+        <v>7015632</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,6 +1223,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack vanligt i området.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 58896-2024 artfynd.xlsx
+++ b/artfynd/A 58896-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121571997</v>
+        <v>121572309</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473779</v>
+        <v>473725</v>
       </c>
       <c r="R2" t="n">
-        <v>7015441</v>
+        <v>7015461</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetade stående döda granar.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121572309</v>
+        <v>121571997</v>
       </c>
       <c r="B3" t="n">
-        <v>79234</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,37 +803,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Josvedviken naturskogar, Josvedviken naturskogar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473725</v>
+        <v>473779</v>
       </c>
       <c r="R3" t="n">
-        <v>7015461</v>
+        <v>7015441</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetade stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121572058</v>
+        <v>121574426</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473765</v>
+        <v>473705</v>
       </c>
       <c r="R5" t="n">
-        <v>7015453</v>
+        <v>7015632</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,24 +1098,14 @@
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om skalade granar. Uppenbart revir.</t>
+          <t>Barkflag/ringhack vanligt i området.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121574426</v>
+        <v>121572058</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1187,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473705</v>
+        <v>473765</v>
       </c>
       <c r="R6" t="n">
-        <v>7015632</v>
+        <v>7015453</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,14 +1210,24 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barkflag/ringhack vanligt i området.</t>
+          <t>Gott om skalade granar. Uppenbart revir.</t>
         </is>
       </c>
       <c r="AD6" t="b">
